--- a/artfynd/A 19418-2023 artfynd.xlsx
+++ b/artfynd/A 19418-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19418-2023 artfynd.xlsx
+++ b/artfynd/A 19418-2023 artfynd.xlsx
@@ -3051,7 +3051,7 @@
         <v>110953257</v>
       </c>
       <c r="B23" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615975.4074190812</v>
+        <v>615975</v>
       </c>
       <c r="R23" t="n">
-        <v>6895563.448227111</v>
+        <v>6895563</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3121,19 +3121,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 19418-2023 artfynd.xlsx
+++ b/artfynd/A 19418-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110953259</v>
+        <v>110953250</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615959.8594394969</v>
+        <v>615977</v>
       </c>
       <c r="R2" t="n">
-        <v>6895539.0712016</v>
+        <v>6895513</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110953218</v>
+        <v>110953224</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616018.220269895</v>
+        <v>616090</v>
       </c>
       <c r="R3" t="n">
-        <v>6895570.998490203</v>
+        <v>6895476</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110953214</v>
+        <v>110953244</v>
       </c>
       <c r="B4" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616007.3931921899</v>
+        <v>616308</v>
       </c>
       <c r="R4" t="n">
-        <v>6895640.749268921</v>
+        <v>6895256</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,19 +937,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110953255</v>
+        <v>110953248</v>
       </c>
       <c r="B5" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615983.5801135194</v>
+        <v>616022</v>
       </c>
       <c r="R5" t="n">
-        <v>6895543.627030319</v>
+        <v>6895471</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,19 +1034,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110953252</v>
+        <v>110953251</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615929.5799228094</v>
+        <v>615937</v>
       </c>
       <c r="R6" t="n">
-        <v>6895561.87227981</v>
+        <v>6895523</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,24 +1131,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110953244</v>
+        <v>110953258</v>
       </c>
       <c r="B7" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616308.1349809984</v>
+        <v>615975</v>
       </c>
       <c r="R7" t="n">
-        <v>6895255.594064021</v>
+        <v>6895563</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1313,19 +1228,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110953237</v>
+        <v>112038604</v>
       </c>
       <c r="B8" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616161.1266557055</v>
+        <v>615977</v>
       </c>
       <c r="R8" t="n">
-        <v>6895268.760921733</v>
+        <v>6895550</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110953246</v>
+        <v>110953229</v>
       </c>
       <c r="B9" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616295.6869263211</v>
+        <v>616120</v>
       </c>
       <c r="R9" t="n">
-        <v>6895290.697615654</v>
+        <v>6895452</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1537,27 +1422,18 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1576,37 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110953256</v>
+        <v>110953242</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615985.5488361627</v>
+        <v>616294</v>
       </c>
       <c r="R10" t="n">
-        <v>6895554.447164084</v>
+        <v>6895292</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,27 +1520,18 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1688,37 +1550,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110953223</v>
+        <v>112038596</v>
       </c>
       <c r="B11" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1585,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616026.5843504887</v>
+        <v>616076</v>
       </c>
       <c r="R11" t="n">
-        <v>6895532.01660173</v>
+        <v>6895428</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1758,27 +1615,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>50 bladrosetter</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,15 +1647,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110953250</v>
+        <v>112038600</v>
       </c>
       <c r="B12" t="n">
-        <v>77550</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,21 +1658,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>4412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1682,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615977.1580437272</v>
+        <v>616034</v>
       </c>
       <c r="R12" t="n">
-        <v>6895512.551193926</v>
+        <v>6895586</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1875,22 +1712,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,15 +1744,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110953251</v>
+        <v>112038602</v>
       </c>
       <c r="B13" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,21 +1755,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>4412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615937.0077223382</v>
+        <v>616027</v>
       </c>
       <c r="R13" t="n">
-        <v>6895522.857952732</v>
+        <v>6895554</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1987,22 +1809,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,37 +1841,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110953238</v>
+        <v>110953220</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>616229.0020581052</v>
+        <v>616041</v>
       </c>
       <c r="R14" t="n">
-        <v>6895255.670926915</v>
+        <v>6895562</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2102,24 +1909,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>50 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,37 +1938,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110953217</v>
+        <v>110953227</v>
       </c>
       <c r="B15" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +1973,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615993.9554616741</v>
+        <v>616091</v>
       </c>
       <c r="R15" t="n">
-        <v>6895595.875708669</v>
+        <v>6895480</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2219,24 +2006,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,37 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110953226</v>
+        <v>110953255</v>
       </c>
       <c r="B16" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2303,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>616087.0828292217</v>
+        <v>615984</v>
       </c>
       <c r="R16" t="n">
-        <v>6895501.841300109</v>
+        <v>6895544</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2336,19 +2103,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,37 +2132,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110953248</v>
+        <v>112038603</v>
       </c>
       <c r="B17" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2415,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616021.6585651333</v>
+        <v>615968</v>
       </c>
       <c r="R17" t="n">
-        <v>6895471.071691271</v>
+        <v>6895405</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2445,22 +2197,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,15 +2229,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110953242</v>
+        <v>112038597</v>
       </c>
       <c r="B18" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,21 +2240,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2527,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616293.7840547037</v>
+        <v>616173</v>
       </c>
       <c r="R18" t="n">
-        <v>6895291.567062381</v>
+        <v>6895355</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2557,22 +2294,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2581,7 +2308,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2600,37 +2326,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110953224</v>
+        <v>110953215</v>
       </c>
       <c r="B19" t="n">
-        <v>85715</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2640,10 +2361,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616090.3212906126</v>
+        <v>616000</v>
       </c>
       <c r="R19" t="n">
-        <v>6895475.772476388</v>
+        <v>6895633</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2673,19 +2394,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2712,37 +2423,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110953220</v>
+        <v>110953221</v>
       </c>
       <c r="B20" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2752,10 +2458,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616041.4553601014</v>
+        <v>616046</v>
       </c>
       <c r="R20" t="n">
-        <v>6895562.448162532</v>
+        <v>6895502</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2785,19 +2491,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,15 +2520,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110953233</v>
+        <v>110953240</v>
       </c>
       <c r="B21" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2840,21 +2531,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2864,10 +2555,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>616172.836706094</v>
+        <v>616302</v>
       </c>
       <c r="R21" t="n">
-        <v>6895295.813811252</v>
+        <v>6895288</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2897,19 +2588,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2936,37 +2617,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110953260</v>
+        <v>110953247</v>
       </c>
       <c r="B22" t="n">
-        <v>73634</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2976,10 +2652,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616040.9925344958</v>
+        <v>616085</v>
       </c>
       <c r="R22" t="n">
-        <v>6895603.10405636</v>
+        <v>6895430</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3009,19 +2685,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,37 +2714,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110953257</v>
+        <v>110953260</v>
       </c>
       <c r="B23" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +2749,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615975</v>
+        <v>616041</v>
       </c>
       <c r="R23" t="n">
-        <v>6895563</v>
+        <v>6895604</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3150,37 +2811,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110953254</v>
+        <v>112038601</v>
       </c>
       <c r="B24" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,10 +2846,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615989.9466183952</v>
+        <v>616013</v>
       </c>
       <c r="R24" t="n">
-        <v>6895521.87359815</v>
+        <v>6895612</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3220,22 +2876,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,15 +2908,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110953258</v>
+        <v>110953246</v>
       </c>
       <c r="B25" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,21 +2919,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3302,10 +2943,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615975.4074190812</v>
+        <v>616295</v>
       </c>
       <c r="R25" t="n">
-        <v>6895563.448227111</v>
+        <v>6895290</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3335,19 +2976,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,15 +3005,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110953221</v>
+        <v>110953243</v>
       </c>
       <c r="B26" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,34 +3016,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>616046.3341982877</v>
+        <v>616304</v>
       </c>
       <c r="R26" t="n">
-        <v>6895502.308674974</v>
+        <v>6895293</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3447,19 +3077,14 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på barrträd</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3486,37 +3111,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110953215</v>
+        <v>110953257</v>
       </c>
       <c r="B27" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3526,10 +3146,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615999.716797427</v>
+        <v>615975</v>
       </c>
       <c r="R27" t="n">
-        <v>6895632.537929806</v>
+        <v>6895563</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3559,19 +3179,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3598,15 +3208,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>110953227</v>
+        <v>110953214</v>
       </c>
       <c r="B28" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,21 +3219,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3638,10 +3243,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>616090.6120883847</v>
+        <v>616007</v>
       </c>
       <c r="R28" t="n">
-        <v>6895480.925066614</v>
+        <v>6895641</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3671,19 +3276,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,37 +3305,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110953232</v>
+        <v>110953235</v>
       </c>
       <c r="B29" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3750,10 +3340,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616114.3572134096</v>
+        <v>616168</v>
       </c>
       <c r="R29" t="n">
-        <v>6895403.200587871</v>
+        <v>6895274</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3783,19 +3373,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,15 +3402,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>110953249</v>
+        <v>110953212</v>
       </c>
       <c r="B30" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,17 +3430,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>616007.3401849193</v>
+        <v>616024</v>
       </c>
       <c r="R30" t="n">
-        <v>6895478.99417598</v>
+        <v>6895608</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3895,19 +3474,14 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>100 bladrosetter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3916,6 +3490,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3934,37 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>110953247</v>
+        <v>110953217</v>
       </c>
       <c r="B31" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3974,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>616084.8821024001</v>
+        <v>615994</v>
       </c>
       <c r="R31" t="n">
-        <v>6895429.769177985</v>
+        <v>6895595</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4007,19 +3577,14 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,37 +3611,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>110953235</v>
+        <v>110953218</v>
       </c>
       <c r="B32" t="n">
-        <v>96265</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4086,10 +3646,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>616167.9647270772</v>
+        <v>616018</v>
       </c>
       <c r="R32" t="n">
-        <v>6895274.139378979</v>
+        <v>6895571</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4119,19 +3679,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4158,15 +3708,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>110953212</v>
+        <v>110953223</v>
       </c>
       <c r="B33" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4191,21 +3736,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>616024.9005734875</v>
+        <v>616027</v>
       </c>
       <c r="R33" t="n">
-        <v>6895608.160149706</v>
+        <v>6895532</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4235,24 +3776,14 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>100 bladrosetter</t>
+          <t>50 bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4261,7 +3792,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4280,37 +3810,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112038603</v>
+        <v>110953226</v>
       </c>
       <c r="B34" t="n">
-        <v>89518</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4320,10 +3845,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>615968</v>
+        <v>616088</v>
       </c>
       <c r="R34" t="n">
-        <v>6895406</v>
+        <v>6895502</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4350,12 +3875,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,37 +3907,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112038602</v>
+        <v>110953232</v>
       </c>
       <c r="B35" t="n">
-        <v>86372</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4422,10 +3942,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>616026</v>
+        <v>616114</v>
       </c>
       <c r="R35" t="n">
-        <v>6895554</v>
+        <v>6895403</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4452,12 +3972,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4484,37 +4004,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112038601</v>
+        <v>110953233</v>
       </c>
       <c r="B36" t="n">
-        <v>73773</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4524,10 +4039,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616013</v>
+        <v>616172</v>
       </c>
       <c r="R36" t="n">
-        <v>6895612</v>
+        <v>6895296</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4554,12 +4069,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4586,37 +4101,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112038600</v>
+        <v>110953238</v>
       </c>
       <c r="B37" t="n">
-        <v>86372</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4626,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616034</v>
+        <v>616229</v>
       </c>
       <c r="R37" t="n">
-        <v>6895585</v>
+        <v>6895256</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4656,12 +4166,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>50 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4688,37 +4203,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112038599</v>
+        <v>110953249</v>
       </c>
       <c r="B38" t="n">
-        <v>89572</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4728,10 +4238,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>616070</v>
+        <v>616008</v>
       </c>
       <c r="R38" t="n">
-        <v>6895500</v>
+        <v>6895479</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4758,12 +4268,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4790,37 +4300,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112038596</v>
+        <v>110953252</v>
       </c>
       <c r="B39" t="n">
-        <v>90236</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4830,10 +4335,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>616076</v>
+        <v>615929</v>
       </c>
       <c r="R39" t="n">
-        <v>6895428</v>
+        <v>6895562</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4860,12 +4365,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4892,15 +4402,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112038604</v>
+        <v>110953254</v>
       </c>
       <c r="B40" t="n">
-        <v>89994</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4908,21 +4413,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4932,10 +4437,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>615978</v>
+        <v>615990</v>
       </c>
       <c r="R40" t="n">
-        <v>6895550</v>
+        <v>6895522</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4962,12 +4467,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4991,6 +4496,500 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>110953256</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>615985</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6895555</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>110953259</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>615960</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6895540</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>110953230</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>616129</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6895425</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>50 st</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>110953237</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>616161</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6895269</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>112038598</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92285</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6331024</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Skeletocutis delicata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Miettinen &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>616317</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6895256</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Möjligen den nyligen upptäckta S. delicata. Ej mikroskoperad.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19418-2023 artfynd.xlsx
+++ b/artfynd/A 19418-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953250</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953224</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953244</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953248</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953251</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953258</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038604</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953229</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1547,6 +1592,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953242</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1644,6 +1694,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038596</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1741,6 +1796,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038600</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1838,6 +1898,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038602</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1935,6 +2000,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953220</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2032,6 +2102,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953227</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2129,6 +2204,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953255</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2226,6 +2306,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038603</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2323,6 +2408,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038597</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2420,6 +2510,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953215</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2517,6 +2612,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953221</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2614,6 +2714,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953240</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2711,6 +2816,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953247</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2808,6 +2918,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953260</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2905,6 +3020,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038601</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3002,6 +3122,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953246</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3108,6 +3233,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953243</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3205,6 +3335,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953257</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3302,6 +3437,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953214</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3399,6 +3539,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953235</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3506,6 +3651,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953212</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3608,6 +3758,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953217</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3705,6 +3860,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953218</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3807,6 +3967,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953223</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3904,6 +4069,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953226</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4001,6 +4171,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953232</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4098,6 +4273,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953233</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4200,6 +4380,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953238</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4297,6 +4482,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953249</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4399,6 +4589,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953252</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4496,6 +4691,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953254</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4593,6 +4793,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953256</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4690,6 +4895,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953259</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4792,6 +5002,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953230</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4889,6 +5104,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110953237</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4990,8 +5210,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038598</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>